--- a/artfynd/A 40686-2023 artfynd.xlsx
+++ b/artfynd/A 40686-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40686-2023 artfynd.xlsx
+++ b/artfynd/A 40686-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102458067</v>
+        <v>102458066</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -728,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379033.4372923273</v>
+        <v>379033</v>
       </c>
       <c r="R2" t="n">
-        <v>6287343.043528091</v>
+        <v>6287343</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,19 +748,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102458043</v>
+        <v>102458067</v>
       </c>
       <c r="B3" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,23 +789,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379033.4372923273</v>
+        <v>379033</v>
       </c>
       <c r="R3" t="n">
-        <v>6287343.043528091</v>
+        <v>6287343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +859,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102458066</v>
+        <v>102458042</v>
       </c>
       <c r="B4" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,28 +900,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379033.4372923273</v>
+        <v>379033</v>
       </c>
       <c r="R4" t="n">
-        <v>6287343.043528091</v>
+        <v>6287343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,19 +965,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102458042</v>
+        <v>102458043</v>
       </c>
       <c r="B5" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,28 +1006,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220686</v>
+        <v>224364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1080,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379033.4372923273</v>
+        <v>379033</v>
       </c>
       <c r="R5" t="n">
-        <v>6287343.043528091</v>
+        <v>6287343</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,19 +1063,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 40686-2023 artfynd.xlsx
+++ b/artfynd/A 40686-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102458066</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102458067</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102458042</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,8 +1110,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102458043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>